--- a/testFile/case/DriverExcel.xlsx
+++ b/testFile/case/DriverExcel.xlsx
@@ -4,21 +4,33 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17475" windowHeight="8062"/>
+    <workbookView windowWidth="20317" windowHeight="9727" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="employee" sheetId="1" r:id="rId1"/>
     <sheet name="face" sheetId="2" r:id="rId2"/>
     <sheet name="study" sheetId="3" r:id="rId3"/>
-    <sheet name="bus" sheetId="4" r:id="rId4"/>
-    <sheet name="user" sheetId="5" r:id="rId5"/>
+    <sheet name="user" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="255">
   <si>
     <t>测试用例编号</t>
   </si>
@@ -372,18 +384,21 @@
   </si>
   <si>
     <t>{
-  "current": 1,
-  "perSize": 20,
+  "current": 0,
+  "emotions": "",
   "empNameOrJobId": "刘珂珂",
-  "orgNumList": [
-    "100016"
-  ],
+  "healthCode": "",
+  "healthType": true,
+  "icCard": "90359035",
+  "icHardCard": "",
+  "nucleicResult": 0,
+  "orderBy": "",
+  "orgNumList": [],
+  "perSize": 0,
+  "phoneNum": "",
+  "reportCumulativeOverHour": 0,
   "routeName": "",
-  "healthCode": "",
-  "nucleicResult": null,
-  "orderBy": "",
-  "icCard": "90179035",
-  "phoneNum": ""
+  "sampleCumulativeOverHour": 0
 }</t>
   </si>
   <si>
@@ -392,19 +407,19 @@
   "retmsg": "操作成功",
   "data": [
     {
-      "id": 252580,
-      "jobId": "90179035",
+      "id": 372653,
+      "jobId": "90359035",
       "oldJobId": null,
-      "empName": "刘珂珂1",
-      "idCard": "412829199807070099",
-      "icCard": "90179035",
-      "icHardCard": "3846586563",
-      "telephone": "15290179035",
+      "empName": "刘珂珂2",
+      "idCard": "412829199903050503",
+      "icCard": "90359035",
+      "icHardCard": null,
+      "telephone": "15290359035",
       "orgNum": "100016",
       "orgName": "测试部车队",
       "ownRouteName": null,
       "ownRouteId": null,
-      "role": "EMPLOYEE",
+      "role": "DRIVER",
       "sex": null,
       "licenseStartDate": null,
       "drivingExperience": null,
@@ -417,9 +432,10 @@
       "reportOverFlag": false,
       "nucleicResult": null,
       "nucleicResultName": null,
-      "healthCode": "绿码",
-      "healthRefreshTime": "2022-10-27 01:16:23",
-      "isFaceLib": true
+      "healthCode": null,
+      "healthRefreshTime": null,
+      "isFaceLib": false,
+      "healthType": true
     }
   ],
   "total": 1,
@@ -427,9 +443,6 @@
 }</t>
   </si>
   <si>
-    <t>"empName":"刘珂珂1"</t>
-  </si>
-  <si>
     <t>司机信息模糊查询</t>
   </si>
   <si>
@@ -448,11 +461,11 @@
   "retmsg": "操作成功",
   "data": [
     {
-      "empId": "1624506313031",
+      "empId": "1717066517310",
       "jobId": "90179035",
-      "empName": "刘珂珂1",
-      "orgNum": "100016",
-      "orgName": "测试部车队"
+      "empName": "刘珂珂",
+      "orgNum": "55151104151106957047",
+      "orgName": "102车队"
     }
   ],
   "total": 3,
@@ -855,134 +868,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>人车一致业务/报道计划</t>
-  </si>
-  <si>
-    <t>多查报道计划</t>
-  </si>
-  <si>
-    <t>/buswash/emp/bus/attend/batch</t>
-  </si>
-  <si>
-    <t>{
-   "Content-Type":"application/x-www-form-urlencoded",
-   "token":"9b8b6005bdb6418a9f70079412dc98c7"
-}</t>
-  </si>
-  <si>
-    <t>智汇笃行小程序端-查询司机排班计划</t>
-  </si>
-  <si>
-    <t>人车一致业务/人车一致记录</t>
-  </si>
-  <si>
-    <t>导出人车一致记录</t>
-  </si>
-  <si>
-    <t>/buswash/emp/bus/attend/export</t>
-  </si>
-  <si>
-    <t>{
-  "current": 0,
-  "date": {
-    "dateEnd": "2023-09-18",
-    "dateStart": "2023-09-18"
-  },
-  "empNameOrJobId": "",
-  "orgNumList": [],
-  "perSize": 0,
-  "planBusNumber": "",
-  "state": 0
-}</t>
-  </si>
-  <si>
-    <t>分页查询人车一致记录</t>
-  </si>
-  <si>
-    <t>/buswash/emp/bus/attend/search</t>
-  </si>
-  <si>
-    <t>单查报道计划</t>
-  </si>
-  <si>
-    <t>/buswash/emp/bus/attend/single</t>
-  </si>
-  <si>
-    <t>{
-   "Content-Type":"application/json",
-   "token":"b541d1f4330941f2ae6c6b3f1cc631fd"
-}</t>
-  </si>
-  <si>
-    <t>{
-  "attendId": null
-}</t>
-  </si>
-  <si>
-    <t>{
-  "retcode": "0",
-  "retmsg": "操作成功",
-  "data": {
-    "attendId": 33943637,
-    "recordDate": "2023-09-18",
-    "shiftNum": "1",
-    "busClass": "6",
-    "jobId": "11100408",
-    "empName": "刘智",
-    "routeId": "3301000100123308",
-    "routeName": "1225M路",
-    "planBusNumber": "1-9005",
-    "planPlateNum": "浙A07655D",
-    "siteId": 3,
-    "onBusAttendScheduleTime": "2023-09-18 05:53:00",
-    "type": "OPERATE",
-    "busNumber": null,
-    "plateNum": null,
-    "state": null,
-    "siteName": "池华街公交站",
-    "busClassName": "高峰班-上",
-    "scheduleTime": "2023-09-18 05:53:00",
-    "recommend": false
-  },
-  "total": null,
-  "success": true
-}</t>
-  </si>
-  <si>
-    <t>"empName":"刘智"</t>
-  </si>
-  <si>
-    <t>人车一致业务/人车一致检查</t>
-  </si>
-  <si>
-    <t>人车一致检查</t>
-  </si>
-  <si>
-    <t>/buswash/emp/bus/check/upload</t>
-  </si>
-  <si>
-    <t>{
-  "attendId": 33943637,
-  "busNumber": "1-9005",
-  "busPlateNum": "浙A07655D"
-}</t>
-  </si>
-  <si>
-    <t>{
-  "retcode": "0",
-  "retmsg": "操作成功",
-  "data": {
-    "planPlateNum": "浙A07655D",
-    "planBusNumber": "1-9005",
-    "plateNum": "浙A07655D",
-    "busNumber": "1-9005",
-    "state": 1
-  },
-  "total": null,
-  "success": true
-}</t>
   </si>
   <si>
     <t>用户模块/卡校验</t>
@@ -1416,44 +1301,15 @@
   </si>
   <si>
     <t>{
-  "retcode": "0",
-  "retmsg": "操作成功",
-  "data": {
-    "id": 121074,
-    "phone": "18028636978",
-    "account": "ceshilkk",
-    "jobNumber": "90909090",
-    "card": null,
-    "department": null,
-    "smsStatus": "DISABLE",
-    "smsTypeList": null,
-    "siteId": 14,
-    "status": 1,
-    "siteName": "九和路停车场",
-    "orgNum": "55151104125204140112",
-    "orgName": "五公司",
-    "name": "测试lkk",
-    "roleList": [
-      {
-        "id": 270,
-        "name": "刘珂珂",
-        "siteId": 1,
-        "description": "刘珂珂",
-        "level": 30,
-        "remark": "测试",
-        "permissionList": null,
-        "createTime": "2021-03-18 10:19:29",
-        "updateTime": "2023-05-30 10:12:38"
-      }
-    ],
-    "userSmsTypeMapList": [],
-    "level": 30,
-    "createTime": "2023-09-25",
-    "updateTime": "2023-09-25"
-  },
+  "retcode": "210000",
+  "retmsg": "用户手机号重复",
+  "data": null,
   "total": null,
-  "success": true
-}</t>
+  "success": false
+}</t>
+  </si>
+  <si>
+    <t>"retmsg":"用户手机号重复"</t>
   </si>
   <si>
     <t>用户模块/组织权限用户</t>
@@ -1607,6 +1463,33 @@
     "pages": 0,
     "total": 1,
     "records": []
+  },
+  "total": null,
+  "success": true
+}</t>
+  </si>
+  <si>
+    <t>更新检查员</t>
+  </si>
+  <si>
+    <t>/buswash/user/inspector/update</t>
+  </si>
+  <si>
+    <t>{
+  "id": 0,
+  "jobNumber": "",
+  "name": "测试小刘",
+  "phone": "15290179090",
+  "token": "c5def5e2fab84b80ad412fd2ca6c2e41"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": {
+    "retcode": "10001",
+    "retmsg": "找不到用户"
   },
   "total": null,
   "success": true
@@ -1899,6 +1782,9 @@
     <t>/buswash/user/site/permission/search/tree</t>
   </si>
   <si>
+    <t>获取用户场站权限查询树（可配是否过滤无场站的二级组织）</t>
+  </si>
+  <si>
     <t>/buswash/user/site/permission/search/tree/filter</t>
   </si>
   <si>
@@ -1959,7 +1845,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2569,7 +2455,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2581,6 +2467,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3351,7 +3240,7 @@
         <v>71</v>
       </c>
       <c r="J15" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" ht="142" customHeight="1" spans="1:10">
@@ -3362,28 +3251,28 @@
         <v>62</v>
       </c>
       <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
         <v>73</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" t="s">
-        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16">
+        <v>200</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H16">
-        <v>200</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="J16" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" ht="114" customHeight="1" spans="1:10">
@@ -3394,28 +3283,28 @@
         <v>62</v>
       </c>
       <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
         <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
-        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17">
+        <v>200</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H17">
-        <v>200</v>
-      </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" t="s">
         <v>80</v>
-      </c>
-      <c r="J17" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3480,31 +3369,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>83</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>84</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2">
+        <v>200</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H2">
-        <v>200</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" t="s">
         <v>86</v>
-      </c>
-      <c r="J2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="3" ht="54" spans="1:8">
@@ -3512,16 +3401,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
         <v>88</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>14</v>
@@ -3535,31 +3424,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" t="s">
         <v>91</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
         <v>92</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>93</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4">
+        <v>200</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H4">
-        <v>200</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" t="s">
         <v>95</v>
-      </c>
-      <c r="J4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="5" ht="111" customHeight="1" spans="1:8">
@@ -3567,22 +3456,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
         <v>97</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>98</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H5">
         <v>200</v>
@@ -3593,28 +3482,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
         <v>100</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>101</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6">
+        <v>200</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="H6">
-        <v>200</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="J6" t="s">
         <v>51</v>
@@ -3625,28 +3514,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
         <v>104</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>105</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7">
+        <v>200</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H7">
-        <v>200</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -3657,28 +3546,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" t="s">
         <v>108</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
         <v>109</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>110</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8">
+        <v>200</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="H8">
-        <v>200</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
@@ -3689,28 +3578,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
         <v>113</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>114</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H9">
         <v>200</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -3777,31 +3666,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>117</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2">
+        <v>200</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J2" t="s">
         <v>119</v>
-      </c>
-      <c r="H2">
-        <v>200</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="3" ht="129" customHeight="1" spans="1:10">
@@ -3809,16 +3698,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
         <v>121</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>122</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>45</v>
@@ -3827,7 +3716,7 @@
         <v>200</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -3838,28 +3727,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
         <v>124</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>125</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H4">
         <v>200</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J4" t="s">
         <v>16</v>
@@ -3870,28 +3759,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
         <v>127</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>128</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H5">
         <v>200</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -3902,28 +3791,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
         <v>130</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>131</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6">
+        <v>200</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="H6">
-        <v>200</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -3934,28 +3823,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
         <v>134</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>135</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H7">
         <v>200</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -3966,28 +3855,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
         <v>137</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>138</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8">
         <v>200</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
@@ -3998,28 +3887,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" t="s">
         <v>140</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
         <v>141</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>142</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H9">
         <v>200</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -4030,28 +3919,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
         <v>144</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
-        <v>145</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H10">
         <v>200</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J10" t="s">
         <v>16</v>
@@ -4062,28 +3951,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
         <v>147</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>148</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H11">
+        <v>200</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="H11">
-        <v>200</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -4098,224 +3987,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="5"/>
-  <cols>
-    <col min="1" max="1" width="15.6106194690265" customWidth="1"/>
-    <col min="2" max="2" width="25.6902654867257" customWidth="1"/>
-    <col min="3" max="3" width="22.2389380530973" customWidth="1"/>
-    <col min="4" max="4" width="12.353982300885" customWidth="1"/>
-    <col min="5" max="5" width="38.7699115044248" customWidth="1"/>
-    <col min="6" max="6" width="48.3893805309735" customWidth="1"/>
-    <col min="7" max="7" width="34.2477876106195" customWidth="1"/>
-    <col min="8" max="8" width="16.0088495575221" customWidth="1"/>
-    <col min="9" max="9" width="41.8230088495575" customWidth="1"/>
-    <col min="10" max="10" width="20.3805309734513" customWidth="1"/>
-    <col min="11" max="11" width="14.3451327433628" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="2" ht="87" customHeight="1" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H2">
-        <v>200</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" t="s">
-        <v>120</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="3" ht="118" customHeight="1" spans="1:8">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" ht="127" customHeight="1" spans="1:10">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H4">
-        <v>200</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="J4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" ht="109" customHeight="1" spans="1:10">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H5">
-        <v>200</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="6" ht="136" customHeight="1" spans="1:10">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H6">
-        <v>200</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="J6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.2654867256637" customWidth="1"/>
@@ -4363,7 +4035,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" ht="97" customHeight="1" spans="1:11">
@@ -4371,34 +4043,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="H2">
         <v>200</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="J2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" ht="120" customHeight="1" spans="1:10">
@@ -4406,16 +4078,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>14</v>
@@ -4424,10 +4096,10 @@
         <v>200</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="J3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" ht="132" customHeight="1" spans="1:10">
@@ -4435,16 +4107,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>14</v>
@@ -4453,10 +4125,10 @@
         <v>200</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="J4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" ht="115" customHeight="1" spans="1:10">
@@ -4464,31 +4136,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="D5" t="s">
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="H5">
         <v>200</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="J5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" ht="166" customHeight="1" spans="1:10">
@@ -4496,31 +4168,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="D6" t="s">
         <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="H6">
         <v>200</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="J6" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" ht="139" customHeight="1" spans="1:10">
@@ -4528,31 +4200,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="D7" t="s">
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="H7">
         <v>200</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="J7" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" ht="108" spans="1:10">
@@ -4560,31 +4232,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
         <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="H8">
         <v>200</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" ht="94.5" spans="1:10">
@@ -4592,31 +4264,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H9">
         <v>200</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" ht="135" spans="1:10">
@@ -4624,31 +4296,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="H10">
         <v>200</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="J10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" ht="126" customHeight="1" spans="1:10">
@@ -4656,31 +4328,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="H11">
         <v>200</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="J11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" ht="132" customHeight="1" spans="1:10">
@@ -4688,170 +4360,173 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="H12">
         <v>200</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="J12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" ht="67.5" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" ht="135" spans="1:10">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="D13" t="s">
         <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="H13">
         <v>200</v>
       </c>
-      <c r="I13" t="s">
-        <v>223</v>
+      <c r="I13" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="J13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" ht="54" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" ht="67.5" spans="1:10">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="H14">
         <v>200</v>
       </c>
       <c r="I14" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="J14" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" ht="94.5" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" ht="54" spans="1:10">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>228</v>
+        <v>166</v>
       </c>
       <c r="H15">
         <v>200</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>112</v>
+      <c r="I15" t="s">
+        <v>205</v>
       </c>
       <c r="J15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" ht="109" customHeight="1" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" ht="94.5" spans="1:10">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="H16">
         <v>200</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="J16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" ht="67.5" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" ht="109" customHeight="1" spans="1:10">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="D17" t="s">
         <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>14</v>
@@ -4859,11 +4534,11 @@
       <c r="H17">
         <v>200</v>
       </c>
-      <c r="I17" t="s">
-        <v>223</v>
+      <c r="I17" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="J17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" ht="67.5" spans="1:10">
@@ -4871,16 +4546,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>14</v>
@@ -4889,135 +4564,132 @@
         <v>200</v>
       </c>
       <c r="I18" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="J18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" ht="150" customHeight="1" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" ht="67.5" spans="1:10">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="D19" t="s">
         <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>242</v>
+        <v>14</v>
       </c>
       <c r="H19">
         <v>200</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>243</v>
+      <c r="I19" t="s">
+        <v>205</v>
       </c>
       <c r="J19" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="20" ht="94.5" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" ht="150" customHeight="1" spans="1:10">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="D20" t="s">
         <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="H20">
         <v>200</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>112</v>
+        <v>225</v>
       </c>
       <c r="J20" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" ht="67.5" spans="1:10">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="21" ht="94.5" spans="1:10">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
       </c>
       <c r="E21" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H21">
+        <v>200</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" ht="67.5" spans="1:10">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>233</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H21">
-        <v>200</v>
-      </c>
-      <c r="I21" t="s">
-        <v>223</v>
-      </c>
-      <c r="J21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" ht="54" spans="1:10">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>252</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" t="s">
-        <v>254</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="H22">
         <v>200</v>
       </c>
       <c r="I22" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="J22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" ht="54" spans="1:10">
@@ -5025,28 +4697,31 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D23" t="s">
         <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="G23" s="2" t="s">
+        <v>237</v>
+      </c>
       <c r="H23">
         <v>200</v>
       </c>
       <c r="I23" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="J23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" ht="54" spans="1:10">
@@ -5054,156 +4729,185 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="D24" t="s">
         <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="H24">
         <v>200</v>
       </c>
       <c r="I24" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="J24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" ht="67.5" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" ht="54" spans="1:10">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="D25" t="s">
         <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="H25">
         <v>200</v>
       </c>
       <c r="I25" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="J25" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" ht="54" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" ht="67.5" spans="1:10">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="D26" t="s">
         <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="H26">
         <v>200</v>
       </c>
       <c r="I26" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="J26" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" ht="94.5" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" ht="54" spans="1:10">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="D27" t="s">
         <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>267</v>
+        <v>166</v>
       </c>
       <c r="H27">
         <v>200</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>112</v>
+      <c r="I27" t="s">
+        <v>205</v>
       </c>
       <c r="J27" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" ht="135" spans="1:10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" ht="94.5" spans="1:10">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" t="s">
         <v>249</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" t="s">
-        <v>269</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="H28">
         <v>200</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>271</v>
+        <v>111</v>
       </c>
       <c r="J28" t="s">
-        <v>120</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" ht="135" spans="1:10">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>231</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" t="s">
+        <v>252</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H29">
+        <v>200</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J29" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
